--- a/artfynd/A 49231-2023 artfynd.xlsx
+++ b/artfynd/A 49231-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49231-2023 artfynd.xlsx
+++ b/artfynd/A 49231-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>59143248</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611338.6193241823</v>
+        <v>611339</v>
       </c>
       <c r="R2" t="n">
-        <v>6534115.058579506</v>
+        <v>6534115</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +753,9 @@
           <t>2016-04-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-04-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91940206</v>
+        <v>91940223</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1445</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611323.4328846246</v>
+        <v>611323</v>
       </c>
       <c r="R3" t="n">
-        <v>6534121.3335858</v>
+        <v>6534121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,28 +856,13 @@
           <t>2021-03-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-03-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Negativ påverkan från hygge alldels intill ljusinsläpp och vildsvinsbök</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -922,123 +887,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>91940223</v>
-      </c>
-      <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2180</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Långmossen, söder om vägen, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>611323.4328846246</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6534121.3335858</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Råby-Rönö</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49231-2023 artfynd.xlsx
+++ b/artfynd/A 49231-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59143248</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91940223</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>